--- a/descargas/sya_logistica_requerimientos.xlsx
+++ b/descargas/sya_logistica_requerimientos.xlsx
@@ -425,20 +425,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,19 +462,19 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Stock</t>
@@ -484,34 +482,24 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Adquirido</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Saldo</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
+          <t>Timestamp</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PEDRO</t>
+          <t>Juan Gomez</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>OT67</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -519,34 +507,39 @@
           <t>LAP</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CAJA DE DISCO DE CORTE DE 9"</t>
-        </is>
+      <c r="E2" t="n">
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>22</v>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>caja de disco de desbaste de 4 1/2"</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2025-09-30 18:56:01</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PEDRO</t>
+          <t>Juan Gomez</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>OT67</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -554,438 +547,23 @@
           <t>LAP</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ROTOMARTILLO 9KG</t>
-        </is>
+      <c r="E3" t="n">
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>15/05/2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>JOSE PERALES</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>OT95</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>RDL</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CAJA DE DISCO DE CORTE DE 9"</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>15/05/2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>JOSE PERALES</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>OT95</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>RDL</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LIJA AL AGUA</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>09/05/2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>juan perez</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ot990</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>rdl</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ROTOMARTILLO DE 6.73 KG</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>09/05/2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>juan perez</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ot990</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>rdl</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CAJA DE DISCO DE DESBASTE DE 4 1/2"</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>09/05/2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Jose Gomez</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>OT-889</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LAP</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Lija para fierro</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>09/05/2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Jose Gomez</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>OT-889</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LAP</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>DEMOLEDOR DE 11KG</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>09/05/2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Jose Gomez</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>OT-889</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LAP</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>PUNTA CINCEL PARA DEMOLEDOR Y ROTOMARTILLO</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>09/05/2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>JUSN CSRLOS</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ot67</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>rultas dd lima</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ROTOMARTILLO DE 6.73 KG</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/05/2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>JUSN CSRLOS</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ot67</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>rultas dd lima</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>DISOLVENTE ESPECIAL PARA TRAFICO ANYPSA</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>GLN</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>08/05/2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>JUAN RAMOS</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>OT1222</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>RDL</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CAJA DE DISCO DE DESBASTE DE 4 1/2"</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>08/05/2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>JUAN RAMOS</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>OT1222</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>RDL</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>PARES DE ZAPATO DE CUERO CAÑA ALTA PARA SOLDADOR</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>08/05/2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>JUAN RAMOS</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>OT1222</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>RDL</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AMOLADORA DE 9"</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>5</v>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>puntas para demoledor y rotomartillo</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2025-09-30 18:56:01</t>
+        </is>
       </c>
     </row>
   </sheetData>
